--- a/Documentation/Mediciones Motor.xlsx
+++ b/Documentation/Mediciones Motor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2ce62c51eb142d3/Desktop/EDUARDO DOCS/Investigacion Torque-Velocidad/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2ce62c51eb142d3/Desktop/EDUARDO DOCS/Investigacion Torque-Velocidad/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="8_{E5BC7409-0476-4DAC-8D7B-49AEA39C097C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A17BD93-E751-4A44-A7FD-2399D25BB8CE}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{A7FEB510-BA41-4534-973E-439437F18F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5B8AFA-5CDB-4C37-8285-64EC153EFF5B}"/>
   <bookViews>
-    <workbookView xWindow="12463" yWindow="0" windowWidth="12776" windowHeight="13536" xr2:uid="{1E203277-977B-4F3E-A76D-A9EA142B0A2E}"/>
+    <workbookView xWindow="26" yWindow="26" windowWidth="25109" windowHeight="13405" xr2:uid="{1E203277-977B-4F3E-A76D-A9EA142B0A2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
   <si>
     <t>No.</t>
   </si>
@@ -196,6 +196,36 @@
   </si>
   <si>
     <t>Resistencia Armadura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltaje </t>
+  </si>
+  <si>
+    <t>Corriente</t>
+  </si>
+  <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>Torque (NM)</t>
+  </si>
+  <si>
+    <t>I pr (mA)</t>
+  </si>
+  <si>
+    <t>I re (mA)</t>
+  </si>
+  <si>
+    <t>Dif (mA)</t>
+  </si>
+  <si>
+    <t>Dos motores</t>
+  </si>
+  <si>
+    <t>V_Generado</t>
+  </si>
+  <si>
+    <t>RPM Negro</t>
   </si>
 </sst>
 </file>
@@ -403,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -471,6 +501,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,6 +519,2439 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Corriente</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Sensor vs Corriente Real</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$45</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>I pr (mA)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$46:$A$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$46:$B$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>922</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1085</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8491-4C51-AC55-2F3CFD95F0B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$45</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>I re (mA)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$46:$A$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$46:$C$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1070</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1140</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1260</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8491-4C51-AC55-2F3CFD95F0B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$45</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dif (mA)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$46:$A$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$46:$D$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>175</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8491-4C51-AC55-2F3CFD95F0B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2057029951"/>
+        <c:axId val="1908466159"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2057029951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1908466159"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1908466159"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2057029951"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>Voltaje-Torque (sin carga)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$45</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Torque (NM)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$46:$A$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$46:$E$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2.6209338426279601E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.6786899923605805E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6100907563025209E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.131046692131398</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16817658823529411</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16162425362872421</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1878335920550038</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.21404293048128339</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.24025226890756302</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.27082983040488923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.2926709457601222</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.32324850725744841</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.34945784568372801</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.38003540718105422</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.41061296867838043</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.43682230710466002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.46739986860198623</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.49797743009931239</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.52418676852559198</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55039610695187158</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3E99-4CBE-B28C-0F52263C13FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2057029951"/>
+        <c:axId val="1908466159"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2057029951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1908466159"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1908466159"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2057029951"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1078961</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>57574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>91874</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>141416</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE3AB62C-2AA5-65D6-CF08-3608750438DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1068780</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>101787</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>81693</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>185630</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{849F6128-7622-4F0B-819B-42478AC30761}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -805,11 +3271,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53681071-BEA8-40B0-BD51-3FDAB19EFFE1}">
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="3"/>
+    <col min="5" max="5" width="12.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="3"/>
     <col min="7" max="7" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="8.88671875" style="3"/>
     <col min="12" max="12" width="11.44140625" style="3" bestFit="1" customWidth="1"/>
@@ -1190,6 +3659,10 @@
       <c r="D19" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="I19" s="3">
+        <f>77.7/(R_a+10.3)</f>
+        <v>3.3694709453599305</v>
+      </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
@@ -1324,7 +3797,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
         <v>39</v>
       </c>
@@ -1343,18 +3816,18 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B34" s="14"/>
       <c r="G34" s="15"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B35" s="14"/>
       <c r="C35" s="18">
         <v>0</v>
       </c>
       <c r="G35" s="15"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
         <v>40</v>
       </c>
@@ -1364,11 +3837,11 @@
       </c>
       <c r="G36" s="15"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B37" s="14"/>
       <c r="G37" s="15"/>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B38" s="14" t="s">
         <v>41</v>
       </c>
@@ -1380,11 +3853,11 @@
       </c>
       <c r="G38" s="15"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B39" s="14"/>
       <c r="G39" s="15"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B40" s="14" t="s">
         <v>42</v>
       </c>
@@ -1393,7 +3866,7 @@
       </c>
       <c r="G40" s="15"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B41" s="22"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -1401,7 +3874,482 @@
       <c r="F41" s="23"/>
       <c r="G41" s="24"/>
     </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3">
+        <v>60</v>
+      </c>
+      <c r="D46" s="3">
+        <f>C46-B46</f>
+        <v>60</v>
+      </c>
+      <c r="E46" s="3">
+        <f>Kt*C46/1000</f>
+        <v>2.6209338426279601E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>2</v>
+      </c>
+      <c r="B47" s="3">
+        <v>5</v>
+      </c>
+      <c r="C47" s="3">
+        <v>130</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" ref="D47:D54" si="1">C47-B47</f>
+        <v>125</v>
+      </c>
+      <c r="E47" s="3">
+        <f>Kt*C47/1000</f>
+        <v>5.6786899923605805E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48" s="3">
+        <v>123</v>
+      </c>
+      <c r="C48" s="3">
+        <v>220</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="E48" s="3">
+        <f>Kt*C48/1000</f>
+        <v>9.6100907563025209E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49" s="3">
+        <v>190</v>
+      </c>
+      <c r="C49" s="3">
+        <v>300</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="E49" s="3">
+        <f>Kt*C49/1000</f>
+        <v>0.131046692131398</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" s="3">
+        <v>255</v>
+      </c>
+      <c r="C50" s="3">
+        <v>385</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="E50" s="3">
+        <f>Kt*C50/1000</f>
+        <v>0.16817658823529411</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>6</v>
+      </c>
+      <c r="B51" s="3">
+        <v>250</v>
+      </c>
+      <c r="C51" s="3">
+        <v>370</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="E51" s="3">
+        <f>Kt*C51/1000</f>
+        <v>0.16162425362872421</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>7</v>
+      </c>
+      <c r="B52" s="3">
+        <v>320</v>
+      </c>
+      <c r="C52" s="3">
+        <v>430</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="E52" s="3">
+        <f>Kt*C52/1000</f>
+        <v>0.1878335920550038</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>8</v>
+      </c>
+      <c r="B53" s="3">
+        <v>370</v>
+      </c>
+      <c r="C53" s="3">
+        <v>490</v>
+      </c>
+      <c r="D53" s="3">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="E53" s="3">
+        <f>Kt*C53/1000</f>
+        <v>0.21404293048128339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>9</v>
+      </c>
+      <c r="B54" s="3">
+        <v>425</v>
+      </c>
+      <c r="C54" s="3">
+        <v>550</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="E54" s="3">
+        <f>Kt*C54/1000</f>
+        <v>0.24025226890756302</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>10</v>
+      </c>
+      <c r="B55" s="3">
+        <v>470</v>
+      </c>
+      <c r="C55" s="3">
+        <v>620</v>
+      </c>
+      <c r="D55" s="3">
+        <f>C55-B55</f>
+        <v>150</v>
+      </c>
+      <c r="E55" s="3">
+        <f>Kt*C55/1000</f>
+        <v>0.27082983040488923</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>11</v>
+      </c>
+      <c r="B56" s="3">
+        <v>535</v>
+      </c>
+      <c r="C56" s="3">
+        <v>670</v>
+      </c>
+      <c r="D56" s="3">
+        <f>C56-B56</f>
+        <v>135</v>
+      </c>
+      <c r="E56" s="3">
+        <f>Kt*C56/1000</f>
+        <v>0.2926709457601222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>12</v>
+      </c>
+      <c r="B57" s="3">
+        <v>605</v>
+      </c>
+      <c r="C57" s="3">
+        <v>740</v>
+      </c>
+      <c r="D57" s="3">
+        <f>C57-B57</f>
+        <v>135</v>
+      </c>
+      <c r="E57" s="3">
+        <f>Kt*C57/1000</f>
+        <v>0.32324850725744841</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>13</v>
+      </c>
+      <c r="B58" s="3">
+        <v>670</v>
+      </c>
+      <c r="C58" s="3">
+        <v>800</v>
+      </c>
+      <c r="D58" s="3">
+        <f>C58-B58</f>
+        <v>130</v>
+      </c>
+      <c r="E58" s="3">
+        <f>Kt*C58/1000</f>
+        <v>0.34945784568372801</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>14</v>
+      </c>
+      <c r="B59" s="3">
+        <v>735</v>
+      </c>
+      <c r="C59" s="3">
+        <v>870</v>
+      </c>
+      <c r="D59" s="3">
+        <f>C59-B59</f>
+        <v>135</v>
+      </c>
+      <c r="E59" s="3">
+        <f>Kt*C59/1000</f>
+        <v>0.38003540718105422</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>15</v>
+      </c>
+      <c r="B60" s="3">
+        <v>775</v>
+      </c>
+      <c r="C60" s="3">
+        <v>940</v>
+      </c>
+      <c r="D60" s="3">
+        <f>C60-B60</f>
+        <v>165</v>
+      </c>
+      <c r="E60" s="3">
+        <f>Kt*C60/1000</f>
+        <v>0.41061296867838043</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>16</v>
+      </c>
+      <c r="B61" s="3">
+        <v>860</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D61" s="3">
+        <f>C61-B61</f>
+        <v>140</v>
+      </c>
+      <c r="E61" s="3">
+        <f>Kt*C61/1000</f>
+        <v>0.43682230710466002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>17</v>
+      </c>
+      <c r="B62" s="3">
+        <v>922</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1070</v>
+      </c>
+      <c r="D62" s="3">
+        <f>C62-B62</f>
+        <v>148</v>
+      </c>
+      <c r="E62" s="3">
+        <f>Kt*C62/1000</f>
+        <v>0.46739986860198623</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>18</v>
+      </c>
+      <c r="B63" s="3">
+        <v>970</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1140</v>
+      </c>
+      <c r="D63" s="3">
+        <f>C63-B63</f>
+        <v>170</v>
+      </c>
+      <c r="E63" s="3">
+        <f>Kt*C63/1000</f>
+        <v>0.49797743009931239</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>19</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1050</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1200</v>
+      </c>
+      <c r="D64" s="3">
+        <f>C64-B64</f>
+        <v>150</v>
+      </c>
+      <c r="E64" s="3">
+        <f>Kt*C64/1000</f>
+        <v>0.52418676852559198</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>20</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1085</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1260</v>
+      </c>
+      <c r="D65" s="3">
+        <f>C65-B65</f>
+        <v>175</v>
+      </c>
+      <c r="E65" s="3">
+        <f>Kt*C65/1000</f>
+        <v>0.55039610695187158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>30</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1815</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1970</v>
+      </c>
+      <c r="D66" s="3">
+        <f>C66-B66</f>
+        <v>155</v>
+      </c>
+      <c r="E66" s="3">
+        <f>Kt*C66/1000</f>
+        <v>0.86053994499618025</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="3">
+        <f>AVERAGE(D55:D66)</f>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B69" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B79" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B80" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B81" s="3">
+        <v>1750</v>
+      </c>
+      <c r="C81" s="3">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B82" s="3">
+        <v>500</v>
+      </c>
+      <c r="C82" s="3">
+        <v>23.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>